--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל קונסטנטיני - שירי אהבה</v>
+        <v>ליאב דהן - נלחמתי עלייך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410999&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411006&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל קונסטנטיני - שירי אהבה</v>
+        <v>ליאב דהן - נלחמתי עלייך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
+        <v>ישראל בן חמו - נרדי נתן ריחו</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410998&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411005&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יובל גולד &amp; שירה זלוף - מחר יבוא מחר</v>
+        <v>ישראל בן חמו - נרדי נתן ריחו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
+        <v>ישי מדר - להתקרב אליך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410997&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411004&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>טלי רבקה סימן טוב - יוצאת לדרך</v>
+        <v>ישי מדר - להתקרב אליך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טודיאל - לא ממלא לי ת'נשמה</v>
+        <v>יקיר לנקרי - הלב שלי ז״ל</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410996&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411003&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טודיאל - לא ממלא לי ת'נשמה</v>
+        <v>יקיר לנקרי - הלב שלי ז״ל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>זיו גבאי - מין נהאר לי נפטר</v>
+        <v>יניב בן משיח - בית חם</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410995&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411002&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>זיו גבאי - מין נהאר לי נפטר</v>
+        <v>יניב בן משיח - בית חם</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דקלה תפילין - צלקת שלך על הלב</v>
+        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410994&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411001&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דקלה תפילין - צלקת שלך על הלב</v>
+        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בני קראוס - ממשיך לחיות</v>
+        <v>אלכס - בא אלייך</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410993&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411000&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,88 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בני קראוס - ממשיך לחיות</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410992&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אליאור נונה - מחרוזת מאמי שלי 2026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410991&amp;sid=a9f73d3510d6ec0dda9f234116f7863f</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>איציק שריקי - בָּבָּא לִּיווִי</v>
+        <v>אלכס - בא אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאב דהן - נלחמתי עלייך</v>
+        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411006&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411012&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאב דהן - נלחמתי עלייך</v>
+        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+        <v>שי אוחיון - אלקנה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411005&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411011&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישראל בן חמו - נרדי נתן ריחו</v>
+        <v>שי אוחיון - אלקנה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ישי מדר - להתקרב אליך</v>
+        <v>קורל - בלילות</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411004&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411010&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ישי מדר - להתקרב אליך</v>
+        <v>קורל - בלילות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+        <v>נתנאל פורטל - כפרה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411003&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411009&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-24</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יקיר לנקרי - הלב שלי ז״ל</v>
+        <v>נתנאל פורטל - כפרה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יניב בן משיח - בית חם</v>
+        <v>מוטי אוריאל - עם סגולה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411002&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411008&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-24</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יניב בן משיח - בית חם</v>
+        <v>מוטי אוריאל - עם סגולה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
+        <v>ליאל שרעבי - לא סופרת</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411001&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411007&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-24</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יניב איזנקוט - נשבעתי לך ילדה 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלכס - בא אלייך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411000&amp;sid=f6d6121a1f3ae5b2d7cf636c4a4f6087</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלכס - בא אלייך</v>
+        <v>ליאל שרעבי - לא סופרת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
+        <v>אביעד סהר - הילד שביקשתי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411012&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=394212&amp;sid=c5c5533b3b28611bd1aaa0c50db5f783</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אוחנה - המילים שרציתי לכתוב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי אוחיון - אלקנה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411011&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי אוחיון - אלקנה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל - בלילות</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411010&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל - בלילות</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נתנאל פורטל - כפרה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411009&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נתנאל פורטל - כפרה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מוטי אוריאל - עם סגולה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411008&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מוטי אוריאל - עם סגולה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליאל שרעבי - לא סופרת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411007&amp;sid=4bebb833343feef4c2c80ed0ba7ceb47</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-24</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליאל שרעבי - לא סופרת</v>
+        <v>אביעד סהר - הילד שביקשתי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביעד סהר - הילד שביקשתי קאבר</v>
+        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=394212&amp;sid=c5c5533b3b28611bd1aaa0c50db5f783</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411026&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-25</v>
@@ -469,12 +469,506 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביעד סהר - הילד שביקשתי קאבר</v>
+        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411025&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יובל גיגי - בשבילי נברא העולם</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411024&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יובל גיגי - בשבילי נברא העולם</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>טודיאל - אל תפחד</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411023&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>טודיאל - אל תפחד</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חגי מולה - לא מלאך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411022&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חגי מולה - לא מלאך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>השקוף - מודה אני</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411021&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>השקוף - מודה אני</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>הראל סבג - בשמלה ירוקה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411020&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>הראל סבג - בשמלה ירוקה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>הילה וקנין - מי היה שם באמת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411019&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>הילה וקנין - מי היה שם באמת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>דדי מזרחי - הודעה קטנה ממך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411018&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>דדי מזרחי - הודעה קטנה ממך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אסף בר נתן - לעולם לא שלי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411017&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אסף בר נתן - לעולם לא שלי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אוריה אזערי - לא חוזר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411016&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אוריה אזערי - לא חוזר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אודי דמארי - כולנו יחד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411015&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אודי דמארי - כולנו יחד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אביעד - מי אמר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411014&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אביעד - מי אמר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבי סינואני - כולם יודעים קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411013&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבי סינואני - כולם יודעים קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+        <v>שלומי ימין - כלה שלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411026&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411033&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור יונה - מטורף בלילות &amp; השיר האחרון</v>
+        <v>שלומי ימין - כלה שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411025&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411032&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יונתן סבה - מחרוזת אדון עולם 2026</v>
+        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יובל גיגי - בשבילי נברא העולם</v>
+        <v>עודד מנשרי - טוב ועוד טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411024&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411031&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יובל גיגי - בשבילי נברא העולם</v>
+        <v>עודד מנשרי - טוב ועוד טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טודיאל - אל תפחד</v>
+        <v>עדן מאירי - לב לבן קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411023&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411030&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טודיאל - אל תפחד</v>
+        <v>עדן מאירי - לב לבן קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חגי מולה - לא מלאך</v>
+        <v>נרקיס - שעת רצון</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411022&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411029&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חגי מולה - לא מלאך</v>
+        <v>נרקיס - שעת רצון</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>השקוף - מודה אני</v>
+        <v>ליעד בנאי - צחוק של ילדים</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411021&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411028&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-25</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>השקוף - מודה אני</v>
+        <v>ליעד בנאי - צחוק של ילדים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>הראל סבג - בשמלה ירוקה</v>
+        <v>ליאם גולן - אוהב או שונא</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-25</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411020&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411027&amp;sid=55a05d73587d1c30271d40149943d46a</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-25</v>
@@ -697,278 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>הראל סבג - בשמלה ירוקה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>הילה וקנין - מי היה שם באמת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411019&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>הילה וקנין - מי היה שם באמת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>דדי מזרחי - הודעה קטנה ממך</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411018&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>דדי מזרחי - הודעה קטנה ממך</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אסף בר נתן - לעולם לא שלי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411017&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אסף בר נתן - לעולם לא שלי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אוריה אזערי - לא חוזר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411016&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אוריה אזערי - לא חוזר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אודי דמארי - כולנו יחד</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411015&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אודי דמארי - כולנו יחד</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אביעד - מי אמר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411014&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אביעד - מי אמר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אבי סינואני - כולם יודעים קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411013&amp;sid=bfb9cb20bd62c57794c9ae0ea0e7d8c1</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אבי סינואני - כולם יודעים קאבר</v>
+        <v>ליאם גולן - אוהב או שונא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - כלה שלי</v>
+        <v>עמרם אדר - מברוק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411033&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411045&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - כלה שלי</v>
+        <v>עמרם אדר - מברוק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
+        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411032&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411044&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קורין גמליאל - עם היופי שלי והשכל שלך</v>
+        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עודד מנשרי - טוב ועוד טוב</v>
+        <v>ליאורה יצחק - רואה אותי</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411031&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411043&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עודד מנשרי - טוב ועוד טוב</v>
+        <v>ליאורה יצחק - רואה אותי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עדן מאירי - לב לבן קאבר</v>
+        <v>יונתן שחר - שום דבר בעולם</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411030&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411042&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עדן מאירי - לב לבן קאבר</v>
+        <v>יונתן שחר - שום דבר בעולם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נרקיס - שעת רצון</v>
+        <v>טוני ג'ינו - עלילה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411029&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411041&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נרקיס - שעת רצון</v>
+        <v>טוני ג'ינו - עלילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליעד בנאי - צחוק של ילדים</v>
+        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411028&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411040&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליעד בנאי - צחוק של ילדים</v>
+        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ליאם גולן - אוהב או שונא</v>
+        <v>איתן כהן - אבא</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411027&amp;sid=55a05d73587d1c30271d40149943d46a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411039&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,12 +697,202 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ליאם גולן - אוהב או שונא</v>
+        <v>איתן כהן - אבא</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איילת בוקר - אור השם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411038&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איילת בוקר - אור השם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אוראל דהרי - לב קרוע</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411037&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אוראל דהרי - לב קרוע</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אור קודאי - את לא יודעת</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411036&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אור קודאי - את לא יודעת</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אדיר גץ - לפרוטוקול</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411035&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אדיר גץ - לפרוטוקול</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אדיר גץ - לחצן מצוקה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411034&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אדיר גץ - לחצן מצוקה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמרם אדר - מברוק</v>
+        <v>ישראל ורולקר - ירושלים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411045&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411054&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמרם אדר - מברוק</v>
+        <v>ישראל ורולקר - ירושלים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
+        <v>יוסי שטרית - ילד טוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411044&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411053&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיכל לבייב - אורזת מזוודה - לנשים בלבד</v>
+        <v>יוסי שטרית - ילד טוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאורה יצחק - רואה אותי</v>
+        <v>טודיאל - מתמודד עם הפחד</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411043&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411052&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאורה יצחק - רואה אותי</v>
+        <v>טודיאל - מתמודד עם הפחד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יונתן שחר - שום דבר בעולם</v>
+        <v>טודיאל - לפרוק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411042&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411051&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יונתן שחר - שום דבר בעולם</v>
+        <v>טודיאל - לפרוק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>טוני ג'ינו - עלילה</v>
+        <v>דודא - געגועים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411041&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411050&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>טוני ג'ינו - עלילה</v>
+        <v>דודא - געגועים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
+        <v>אריאל בורסוצקי - לראות רק טוב</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411040&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411049&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-26</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אריאל זילבר - תנו לשמש להפציע (זה יבוא וזה יגיע)</v>
+        <v>אריאל בורסוצקי - לראות רק טוב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איתן כהן - אבא</v>
+        <v>אליה אבוקרט - תלך</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411039&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411048&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-26</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>איתן כהן - אבא</v>
+        <v>אליה אבוקרט - תלך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>איילת בוקר - אור השם</v>
+        <v>אברהם יצחק - תבוא אליי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411038&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411047&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-26</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>איילת בוקר - אור השם</v>
+        <v>אברהם יצחק - תבוא אליי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אוראל דהרי - לב קרוע</v>
+        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
       </c>
       <c r="B10" t="str">
         <v>2026-05-26</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411037&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411046&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-26</v>
@@ -773,126 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אוראל דהרי - לב קרוע</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אור קודאי - את לא יודעת</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411036&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אור קודאי - את לא יודעת</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אדיר גץ - לפרוטוקול</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411035&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אדיר גץ - לפרוטוקול</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אדיר גץ - לחצן מצוקה</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411034&amp;sid=89343f6e5fdaeb0aea812ce39e51778b</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אדיר גץ - לחצן מצוקה</v>
+        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישראל ורולקר - ירושלים</v>
+        <v>שי בן לוי - מנהרת הזמן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411054&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411071&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישראל ורולקר - ירושלים</v>
+        <v>שי בן לוי - מנהרת הזמן</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוסי שטרית - ילד טוב</v>
+        <v>עמית מור - משקר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411053&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411070&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוסי שטרית - ילד טוב</v>
+        <v>עמית מור - משקר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>טודיאל - מתמודד עם הפחד</v>
+        <v>לילך בטאט - בת מלך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411052&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411069&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>טודיאל - מתמודד עם הפחד</v>
+        <v>לילך בטאט - בת מלך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טודיאל - לפרוק</v>
+        <v>בר צברי - ככה באמת</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411051&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411068&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טודיאל - לפרוק</v>
+        <v>בר צברי - ככה באמת</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דודא - געגועים</v>
+        <v>אליאור שמש - נעימת השיכורות</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411050&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411067&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>דודא - געגועים</v>
+        <v>אליאור שמש - נעימת השיכורות</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אריאל בורסוצקי - לראות רק טוב</v>
+        <v>אילן יעקב - האור שבך</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411049&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411066&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אריאל בורסוצקי - לראות רק טוב</v>
+        <v>אילן יעקב - האור שבך</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליה אבוקרט - תלך</v>
+        <v>שלמה בר מארח את אהוד בנאי - צור משלו אכלנו</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411048&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411065&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליה אבוקרט - תלך</v>
+        <v>שלמה בר מארח את אהוד בנאי - צור משלו אכלנו</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אברהם יצחק - תבוא אליי</v>
+        <v>שלומי ימין - געגועים</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411047&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411064&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אברהם יצחק - תבוא אליי</v>
+        <v>שלומי ימין - געגועים</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
+        <v>שילה בן סעדון - חולה אהבה</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411046&amp;sid=cac4ee1744ab35eab3311a4053d39a75</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411063&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,12 +773,316 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אבירם פרחן - מאשאפ רק את &amp; אם את עוד אוהבת</v>
+        <v>שילה בן סעדון - חולה אהבה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>קורל ראובן - לפניך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411062&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>קורל ראובן - לפניך</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>סתיו שמש - היופי שבאמצע</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411061&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>סתיו שמש - היופי שבאמצע</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>מיתר רובין - פרחי אהבה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411060&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>מיתר רובין - פרחי אהבה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>מיקי אוזן - הנגב בוער - שיר האליפות הפועל באר שבע 2025-2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411059&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>מיקי אוזן - הנגב בוער - שיר האליפות הפועל באר שבע 2025-2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>מיכאל חן - למה אני חי</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411058&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>מיכאל חן - למה אני חי</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>מיכאל בן שבת - סיגריה בחלון</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411057&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>מיכאל בן שבת - סיגריה בחלון</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>יניב מדר - דרך ארוכה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411056&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>יניב מדר - דרך ארוכה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>גל שלום - המלכה והמשורר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411055&amp;sid=cc7cab3e4b8ac1f92348c5baf205cb01</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>גל שלום - המלכה והמשורר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>